--- a/docs/adjudication_package_v1.xlsx
+++ b/docs/adjudication_package_v1.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studien-Konkordanz" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sonderfaelle" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rulings_Verdikte" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44922,7 +44923,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Autorenteams/Sample prüfen; ggf. Cluster oder Drop-one</t>
+          <t>Autorenteams/Sample prüfen; ggf. Cluster oder Drop-one — VERDIKT R5: beide behalten, EIN Cluster, Duplikatzelle einmal</t>
         </is>
       </c>
     </row>
@@ -44939,7 +44940,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EMPFEHLUNG: ein Studien-Cluster; WP-Zeilensatz kanonisch, EL 2021 = zitierbare VoR (Lookup); 1 Nicht-Treffer-Zeile prüfen — AUTOR-OK F47a (2026-07-07); Volker bestätigt im Adjudikationsgespräch</t>
+          <t>EMPFEHLUNG: ein Studien-Cluster; WP-Zeilensatz kanonisch, EL 2021 = zitierbare VoR (Lookup); 1 Nicht-Treffer-Zeile prüfen — AUTOR-OK F47a (2026-07-07); Volker bestätigt im Adjudikationsgespräch — VERDIKT R6: Cluster; EL-Zeile add (source=EL2021); 29 Zeilen kanonisch</t>
         </is>
       </c>
     </row>
@@ -44991,6 +44992,241 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>out-of-window; dokumentiert, keine Aufnahme</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Ruling</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Verdikt</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Umsetzung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R1 Devalle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Skalen-Lesart</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>409: |z|=2.32/p=.021; outcome_direction=cost; 3 v10-Vorzeichen drehen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R2 Delis Preis-Reserven</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rein (b)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4 Zeilen bleiben; Tag construct_variant=price-valued</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R3 Eichholtz</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rein</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Grenzformel: Unit = Firma und darunter rein; oberhalb raus. 36 Zeilen bleiben; Tag unit=building/loan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R4 industry-sensitive</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sektorliste + 50% Firm-Years; Grenzfall -&gt; mixed (neues Label)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R5 Sandra/Ofogbe</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>behalten + EIN Cluster</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cluster_id gemeinsam; Duplikat-Korrelation einmal (Sandra, N=1440); Ofogbe-Kopie Tag duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R6 K&amp;V</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>behalten + EIN Cluster</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WP-Satz kanonisch (28) + EL-Zeile add (Tag source=EL2021) = 29; 9 Duplikate einfach; Lookup: EL 2021 = VoR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R7 Atif</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>regulation without/without; Bloomberg=disclosure, Asset4=performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R8 Listen-Semantik</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>geschlossen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>keine Antwort nötig; PRISMA-Prosa label-frei</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>K1 K&amp;V Split-Slope</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rein</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>subsample_dimension=other: slope-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>K2 Luo PSM/ATT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rein</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>estimation_method=other: PSM-ATT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K3 Bhattacharya</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>z=sqrt(Chi2), Vorzeichen aus b; Konfliktzellen bleiben FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>K4 Piechocka</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENTFÄLLT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Datei zeigt volle Statistik (15 r + 5 b/SE/t/p); kein Exit</t>
         </is>
       </c>
     </row>
